--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS0318_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS0318_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,7 +597,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Air-Way FF318 (s5, double-pass 2026-10-15, parts.air-way.com/api/series/5, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0318-08 (ORFS-p020-t02) | MODEL: face-seal tube nut (Brennan FS0318-08): hex S / length h = Air-Way; thread = the face-seal thread of the dash from the open face over 0.47, minor = ASME B1.1 basic minor, the thread pocket to the inner lip face at 0.63, lip bore 0.652 through the back face (measured on the -08 pilot; other sizes need their own STEP); the 0.0046 radial thread relief, the 45deg mouth countersink and the 75deg hex end chamfers NOT modelled (as the 0318 nut); single manufacturer</t>
+          <t>Air-Way FF318 (s5, double-pass 2026-10-15, parts.air-way.com/api/series/5, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0318-08 (ORFS-p020-t02) | MODEL: face-seal tube nut (Brennan FS0318-08): hex S / length h = the row; thread = the face-seal thread of the dash from the open face over 0.47, minor = ASME B1.1 basic minor, the thread pocket to the inner lip face at 0.63, lip bore 0.652 through the back face (measured on BRENNAN_FS0318-08, tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)); the small radial thread relief, the 45deg mouth countersink and the 75deg hex end chamfers NOT modelled (as the 0318 nut); single manufacturer</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -608,6 +608,622 @@
       <c r="V2" t="inlineStr">
         <is>
           <t>FS0318-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS0318-04</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>FS0318-04</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ORFS Tube Nut, 9/16-18 UN-2B, lip bore 0.412</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>FS0318</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>9/16-18 UN-2B (face-seal nut)</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>lip bore 0.412 (tube stop, measured on BRENNAN_FS0318-08)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 (s5, double-pass 2026-10-15, parts.air-way.com/api/series/5, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0318-04 (ORFS-p020-t02) | MODEL: face-seal tube nut (Brennan FS0318-04): hex S / length h = the row; thread = the face-seal thread of the dash from the open face over 0.35, minor = ASME B1.1 basic minor, the thread pocket to the inner lip face at 0.482, lip bore 0.412 through the back face (measured on BRENNAN_FS0318-04, tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)); the small radial thread relief, the 45deg mouth countersink and the 75deg hex end chamfers NOT modelled (as the 0318 nut); single manufacturer</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 = Brennan p20 on nut length, hex (rounding-only differences count as equal) | OMi parts file row 5224 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>FS0318-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS0318-06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6198</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6198</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>FS0318-06</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ORFS Tube Nut, 11/16-16 UN-2B, lip bore 0.532</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>FS0318</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>11/16-16 UN-2B (face-seal nut)</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>lip bore 0.532 (tube stop, measured on BRENNAN_FS0318-08)</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 (s5, double-pass 2026-10-15, parts.air-way.com/api/series/5, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0318-06 (ORFS-p020-t02) | MODEL: face-seal tube nut (Brennan FS0318-06): hex S / length h = the row; thread = the face-seal thread of the dash from the open face over 0.41, minor = ASME B1.1 basic minor, the thread pocket to the inner lip face at 0.552, lip bore 0.532 through the back face (measured on BRENNAN_FS0318-06, tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)); the small radial thread relief, the 45deg mouth countersink and the 75deg hex end chamfers NOT modelled (as the 0318 nut); single manufacturer</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 = Brennan p20 on nut length, hex (rounding-only differences count as equal) | OMi parts file row 5225 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>FS0318-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FS0318-10</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.65241</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.46135</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>FS0318-10</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ORFS Tube Nut, 1-14 UN-2B, lip bore 0.829</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FS0318</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1-14 UN-2B (face-seal nut)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>lip bore 0.829 (tube stop, measured on BRENNAN_FS0318-08)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 (s5, double-pass 2026-10-15, parts.air-way.com/api/series/5, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0318-10 (ORFS-p020-t02) | MODEL: face-seal tube nut (Brennan FS0318-10): hex S / length h = the row; thread = the face-seal thread of the dash from the open face over 0.57, minor = ASME B1.1 basic minor, the thread pocket to the inner lip face at 0.768, lip bore 0.829 through the back face (measured on BRENNAN_FS0318-10, tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)); the small radial thread relief, the 45deg mouth countersink and the 75deg hex end chamfers NOT modelled (as the 0318 nut); single manufacturer</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 = Brennan p20 on nut length, hex (rounding-only differences count as equal) | OMi parts file row 5227 (no dimensions) | BRENNAN DIFFERS: BRENNAN_FS0318-10 has its thread bore at dia 0.8920; the model uses the ASME B1.1 basic minor 0.9227 of 1-14 (the thread of the row) - tell the user; DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>FS0318-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FS0318-12</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.79674</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.0973</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.0973</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.54865</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.59376</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>FS0318-12</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ORFS Tube Nut, 1 3/16-12 UN-2B, lip bore 0.950</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>FS0318</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1 3/16-12 UN-2B (face-seal nut)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>lip bore 0.950 (tube stop, measured on BRENNAN_FS0318-08)</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 (s5, double-pass 2026-10-15, parts.air-way.com/api/series/5, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0318-12 (ORFS-p020-t02) | MODEL: face-seal tube nut (Brennan FS0318-12): hex S / length h = the row; thread = the face-seal thread of the dash from the open face over 0.61, minor = ASME B1.1 basic minor, the thread pocket to the inner lip face at 0.827, lip bore 0.95 through the back face (measured on BRENNAN_FS0318-12, tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)); the small radial thread relief, the 45deg mouth countersink and the 75deg hex end chamfers NOT modelled (as the 0318 nut); single manufacturer</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 = Brennan p20 on nut length, hex (rounding-only differences count as equal) | OMi parts file row 5228 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>FS0318-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FS0318-16</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.94108</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.3473</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.3473</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.67365</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.71876</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>FS0318-16</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ORFS Tube Nut, 1 7/16-12 UN-2B, lip bore 1.144</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FS0318</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1 7/16-12 UN-2B (face-seal nut)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>lip bore 1.144 (tube stop, measured on BRENNAN_FS0318-08)</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 (s5, double-pass 2026-10-15, parts.air-way.com/api/series/5, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0318-16 (ORFS-p020-t02) | MODEL: face-seal tube nut (Brennan FS0318-16): hex S / length h = the row; thread = the face-seal thread of the dash from the open face over 0.63, minor = ASME B1.1 basic minor, the thread pocket to the inner lip face at 0.859, lip bore 1.144 through the back face (measured on BRENNAN_FS0318-16, tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)); the small radial thread relief, the 45deg mouth countersink and the 75deg hex end chamfers NOT modelled (as the 0318 nut); single manufacturer</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 = Brennan p20 on nut length, hex (rounding-only differences count as equal) | OMi parts file row 5229 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>FS0318-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FS0318-20</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.08542</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.5973</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.5973</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.79865</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.84376</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>FS0318-20</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ORFS Tube Nut, 1 11/16-12 UN-2B, lip bore 1.415</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>FS0318</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1 11/16-12 UN-2B (face-seal nut)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>lip bore 1.415 (tube stop, measured on BRENNAN_FS0318-08)</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 (s5, double-pass 2026-10-15, parts.air-way.com/api/series/5, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0318-20 (ORFS-p020-t02) | MODEL: face-seal tube nut (Brennan FS0318-20): hex S / length h = the row; thread = the face-seal thread of the dash from the open face over 0.63, minor = ASME B1.1 basic minor, the thread pocket to the inner lip face at 0.859, lip bore 1.415 through the back face (measured on BRENNAN_FS0318-20, tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)); the small radial thread relief, the 45deg mouth countersink and the 75deg hex end chamfers NOT modelled (as the 0318 nut); single manufacturer</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 = Brennan p20 on nut length, hex (rounding-only differences count as equal) | OMi parts file row 5230 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>FS0318-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FS0318-24</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.9098</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.9098</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9549</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.00001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>FS0318-24</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ORFS Tube Nut, 2-12 UN-2B, lip bore 1.728</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>FS0318</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2-12 UN-2B (face-seal nut)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>lip bore 1.728 (tube stop, measured on BRENNAN_FS0318-08)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 (s5, double-pass 2026-10-15, parts.air-way.com/api/series/5, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p20 FS0318-24 (ORFS-p020-t02) | MODEL: face-seal tube nut (Brennan FS0318-24): hex S / length h = the row; thread = the face-seal thread of the dash from the open face over 0.63, minor = ASME B1.1 basic minor, the thread pocket to the inner lip face at 0.859, lip bore 1.728 through the back face (measured on BRENNAN_FS0318-24, tools/_out/orfs_steps2_20261020/loose_survey.txt (-08: tools/_out/orfs_wp2_20261020/end_lib_08.json)); the small radial thread relief, the 45deg mouth countersink and the 75deg hex end chamfers NOT modelled (as the 0318 nut); single manufacturer</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Air-Way FF318 = Brennan p20 on nut length, hex (rounding-only differences count as equal) | OMi parts file row 5231 (no dimensions) | BRENNAN DIFFERS: BRENNAN_FS0318-24 has its thread bore at dia 1.8170; the model uses the ASME B1.1 basic minor 1.9098 of 2-12 (the thread of the row) - tell the user; DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>FS0318-24</t>
         </is>
       </c>
     </row>

--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS0318_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS0318_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
